--- a/Bloque 1/Tema 2/Actividad 1.xlsx
+++ b/Bloque 1/Tema 2/Actividad 1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C98EAFF-D4C2-4A0C-AAF2-F8D9D7E26A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6396167B-72B4-4FCE-8F8D-AFCFA11A54A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="id-ciudad" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="57">
   <si>
     <t>id-ciudad</t>
   </si>
@@ -167,15 +167,6 @@
   </si>
   <si>
     <t>CLUBES_ESPAÑA</t>
-  </si>
-  <si>
-    <t>Club Juega</t>
-  </si>
-  <si>
-    <t>España</t>
-  </si>
-  <si>
-    <t>Extranjero</t>
   </si>
   <si>
     <t>Entrenador</t>
@@ -224,7 +215,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,12 +231,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF242424"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -255,21 +240,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -309,56 +285,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -749,18 +687,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E9C8F1B-07A1-4598-8DE2-63FF5CD8AA64}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.5703125" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24.140625" customWidth="1"/>
     <col min="9" max="9" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -774,7 +714,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -788,7 +728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -802,7 +742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -816,7 +756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -830,7 +770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -844,7 +784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
@@ -858,7 +798,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -872,7 +812,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -886,7 +826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
@@ -900,7 +840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
@@ -914,7 +854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
@@ -928,7 +868,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -942,310 +882,284 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>30</v>
       </c>
-      <c r="H16" t="s">
+      <c r="E16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:7">
       <c r="A18" s="2">
         <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6"/>
       <c r="E18" s="2">
         <v>1</v>
       </c>
-      <c r="H18" s="2">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="2">
+      <c r="G18" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:7">
       <c r="A19" s="2">
         <v>2</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="2">
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="2">
         <v>2</v>
       </c>
-      <c r="E19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2">
-        <v>2</v>
-      </c>
-      <c r="I19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="2">
+      <c r="G19" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:7">
       <c r="A20" s="2">
         <v>3</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="2">
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="2">
         <v>3</v>
       </c>
-      <c r="E20" s="2">
-        <v>2</v>
-      </c>
-      <c r="H20" s="2">
-        <v>3</v>
-      </c>
-      <c r="I20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="2">
+      <c r="G20" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:7">
       <c r="A21" s="2">
         <v>4</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="2">
+      <c r="C21" s="2">
+        <v>2</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="2">
         <v>4</v>
       </c>
-      <c r="E21" s="2">
-        <v>2</v>
-      </c>
-      <c r="H21" s="2">
-        <v>4</v>
-      </c>
-      <c r="I21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J21" s="2">
+      <c r="G21" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:7">
       <c r="A22" s="2">
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="2">
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="2">
         <v>5</v>
       </c>
-      <c r="E22" s="2">
-        <v>3</v>
-      </c>
-      <c r="H22" s="2">
-        <v>5</v>
-      </c>
-      <c r="I22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J22" s="2">
+      <c r="G22" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:7">
       <c r="A23" s="2">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="2">
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" s="2">
         <v>6</v>
       </c>
-      <c r="E23" s="2">
-        <v>3</v>
-      </c>
-      <c r="H23" s="2">
-        <v>6</v>
-      </c>
-      <c r="I23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J23" s="2">
+      <c r="G23" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:7">
       <c r="A24" s="2">
         <v>7</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="2">
+      <c r="C24" s="2">
+        <v>4</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="2">
         <v>7</v>
       </c>
-      <c r="E24" s="2">
-        <v>4</v>
-      </c>
-      <c r="H24" s="2">
-        <v>7</v>
-      </c>
-      <c r="I24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="2">
+      <c r="G24" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:7">
       <c r="A25" s="2">
         <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="2">
+      <c r="C25" s="2">
+        <v>4</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="2">
         <v>8</v>
       </c>
-      <c r="E25" s="2">
-        <v>4</v>
-      </c>
-      <c r="H25" s="2">
-        <v>8</v>
-      </c>
-      <c r="I25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J25" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="2">
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="2">
+      <c r="C26" s="2">
+        <v>5</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="2">
         <v>9</v>
       </c>
-      <c r="E26" s="2">
-        <v>5</v>
-      </c>
-      <c r="H26" s="2">
-        <v>9</v>
-      </c>
-      <c r="I26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J26" s="2">
+      <c r="G26" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:7">
       <c r="A27" s="2">
         <v>10</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="2">
+      <c r="C27" s="2">
+        <v>5</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="2">
         <v>10</v>
       </c>
-      <c r="E27" s="2">
-        <v>5</v>
-      </c>
-      <c r="H27" s="2">
-        <v>10</v>
-      </c>
-      <c r="I27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J27" s="2">
+      <c r="G27" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:7">
       <c r="A28" s="2">
         <v>11</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="2">
+      <c r="C28" s="2">
+        <v>6</v>
+      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" s="2">
         <v>11</v>
       </c>
-      <c r="E28" s="2">
-        <v>6</v>
-      </c>
-      <c r="H28" s="2">
-        <v>11</v>
-      </c>
-      <c r="I28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J28" s="2">
+      <c r="G28" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:7">
       <c r="A29" s="2">
         <v>12</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="2">
+      <c r="C29" s="2">
+        <v>6</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="2">
         <v>12</v>
       </c>
-      <c r="E29" s="2">
-        <v>6</v>
-      </c>
-      <c r="H29" s="2">
-        <v>12</v>
-      </c>
-      <c r="I29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J29" s="2">
+      <c r="G29" s="2">
         <v>2</v>
       </c>
     </row>
@@ -1256,17 +1170,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD350F3-0344-45F3-A2CD-D3354275580F}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
     <col min="2" max="2" width="18.140625" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -1280,7 +1196,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1294,7 +1210,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:10">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1308,7 +1224,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:10">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1322,7 +1238,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:10">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1336,7 +1252,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:10">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1350,7 +1266,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:10">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1364,55 +1280,117 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:10">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="7">
-        <v>1</v>
-      </c>
-      <c r="C11" s="7">
+      <c r="B11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1902</v>
+      </c>
+      <c r="G12" s="2">
+        <v>6</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2">
         <v>2</v>
       </c>
-      <c r="D11" s="7">
+      <c r="B13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2">
         <v>3</v>
       </c>
-      <c r="E11" s="7">
+      <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2">
         <v>4</v>
       </c>
-      <c r="F11" s="6">
+      <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2">
         <v>5</v>
       </c>
-      <c r="G11" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" t="s">
-        <v>45</v>
+      <c r="B16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="2">
+        <v>4</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1919</v>
       </c>
     </row>
   </sheetData>
@@ -1431,7 +1409,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
@@ -1440,7 +1418,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -1448,7 +1426,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -1456,7 +1434,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
@@ -1464,7 +1442,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
@@ -1472,7 +1450,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -1480,7 +1458,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
@@ -1502,7 +1480,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
@@ -1511,7 +1489,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -1519,7 +1497,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -1527,7 +1505,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
@@ -1535,7 +1513,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
@@ -1543,7 +1521,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -1551,7 +1529,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
